--- a/Encoding_B.xlsx
+++ b/Encoding_B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Fernanda/Library/CloudStorage/Box-Box/Leal Lab/Shared Resources/New Emotional Image Sets/A+B NEW/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc151/Library/CloudStorage/Box-Box/Leal Lab/Shared Resources/New Emotional Image Sets/Emotional MDT_A+B Sets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCEEDB5-AB77-E649-A6EA-E2DBA76EF273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D432C27-A42C-E646-9A07-D1EAD797E907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3700" yWindow="5680" windowWidth="27800" windowHeight="16520" xr2:uid="{ADF94288-C02A-494A-88CC-1911B3E65676}"/>
+    <workbookView xWindow="3700" yWindow="5680" windowWidth="18380" windowHeight="16520" xr2:uid="{ADF94288-C02A-494A-88CC-1911B3E65676}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
     <t>1077_C_X.jpg</t>
   </si>
   <si>
-    <t>20022a.jpg</t>
-  </si>
-  <si>
     <t>3080_C_X.jpg</t>
   </si>
   <si>
@@ -229,9 +226,6 @@
     <t>2037_A_L.jpg</t>
   </si>
   <si>
-    <t>10014a.jpg</t>
-  </si>
-  <si>
     <t>1027_A_H.jpg</t>
   </si>
   <si>
@@ -322,9 +316,6 @@
     <t>3038_A_L.jpg</t>
   </si>
   <si>
-    <t>353A.jpg</t>
-  </si>
-  <si>
     <t>1059_A_H.jpg</t>
   </si>
   <si>
@@ -337,9 +328,6 @@
     <t>1074_C_X.jpg</t>
   </si>
   <si>
-    <t>20019a.jpg</t>
-  </si>
-  <si>
     <t>3041_A_H.jpg</t>
   </si>
   <si>
@@ -370,9 +358,6 @@
     <t>3077_C_X.jpg</t>
   </si>
   <si>
-    <t>40010a.jpg</t>
-  </si>
-  <si>
     <t>1009_A_H.jpg</t>
   </si>
   <si>
@@ -397,10 +382,25 @@
     <t>3052_A_H.jpg</t>
   </si>
   <si>
-    <t>235A.jpg</t>
-  </si>
-  <si>
     <t>1004_A_H.jpg</t>
+  </si>
+  <si>
+    <t>1084_C_X.jpg</t>
+  </si>
+  <si>
+    <t>2034_A_L.jpg</t>
+  </si>
+  <si>
+    <t>2020_A_H.jpg</t>
+  </si>
+  <si>
+    <t>2017_A_L.jpg</t>
+  </si>
+  <si>
+    <t>1078_C_X.jpg</t>
+  </si>
+  <si>
+    <t>1082_C_X.jpg</t>
   </si>
 </sst>
 </file>
@@ -424,8 +424,9 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -457,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -468,11 +469,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -890,24 +894,24 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
@@ -918,35 +922,35 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>105</v>
+      <c r="A6" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>4</v>
@@ -960,38 +964,38 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>6</v>
@@ -1002,24 +1006,24 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>6</v>
@@ -1029,8 +1033,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>11</v>
+      <c r="A12" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>3</v>
@@ -1039,99 +1043,99 @@
         <v>6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>7</v>
@@ -1142,7 +1146,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>3</v>
@@ -1151,21 +1155,21 @@
         <v>6</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -1184,52 +1188,52 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>6</v>
@@ -1240,7 +1244,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>3</v>
@@ -1254,24 +1258,24 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>7</v>
@@ -1281,95 +1285,95 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>83</v>
+      <c r="A30" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>7</v>
@@ -1380,35 +1384,35 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>5</v>
@@ -1417,12 +1421,12 @@
         <v>6</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>5</v>
@@ -1431,57 +1435,57 @@
         <v>6</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>121</v>
+      <c r="A41" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>28</v>
+      <c r="A43" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>6</v>
@@ -1492,21 +1496,21 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>3</v>
@@ -1520,7 +1524,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>5</v>
@@ -1529,12 +1533,12 @@
         <v>6</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>5</v>
@@ -1548,7 +1552,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>4</v>
@@ -1557,71 +1561,71 @@
         <v>6</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>9</v>
+      <c r="A53" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>7</v>
@@ -1632,35 +1636,35 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>4</v>
@@ -1674,38 +1678,38 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>7</v>
@@ -1716,66 +1720,66 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="4" t="s">
-        <v>111</v>
+      <c r="A65" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>7</v>
@@ -1785,22 +1789,22 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="5" t="s">
-        <v>12</v>
+      <c r="A66" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>3</v>
@@ -1809,15 +1813,15 @@
         <v>6</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>6</v>
@@ -1827,22 +1831,22 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
-        <v>115</v>
+      <c r="A69" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>3</v>
@@ -1856,7 +1860,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>3</v>
@@ -1865,12 +1869,12 @@
         <v>6</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>4</v>
@@ -1884,7 +1888,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>3</v>
@@ -1893,15 +1897,15 @@
         <v>6</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
-        <v>101</v>
+      <c r="A74" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>6</v>
@@ -1912,38 +1916,38 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>6</v>
@@ -1953,8 +1957,8 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
-        <v>64</v>
+      <c r="A78" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>3</v>
@@ -1968,24 +1972,24 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>7</v>
@@ -1996,24 +2000,24 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>6</v>
@@ -2024,24 +2028,24 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>6</v>
@@ -2052,38 +2056,38 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>6</v>
@@ -2094,24 +2098,24 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>6</v>
@@ -2122,24 +2126,24 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>7</v>
@@ -2149,22 +2153,22 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="2" t="s">
-        <v>31</v>
+      <c r="A92" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>3</v>
@@ -2177,8 +2181,8 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="3" t="s">
-        <v>120</v>
+      <c r="A94" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>4</v>
@@ -2191,11 +2195,11 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
-        <v>117</v>
+      <c r="A95" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>6</v>
@@ -2206,38 +2210,38 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>6</v>
@@ -2247,22 +2251,22 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="2" t="s">
-        <v>30</v>
+      <c r="A99" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>4</v>
@@ -2271,26 +2275,26 @@
         <v>6</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>3</v>
@@ -2304,24 +2308,24 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>6</v>
@@ -2331,11 +2335,11 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="3" t="s">
-        <v>95</v>
+      <c r="A105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>7</v>
@@ -2346,66 +2350,66 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>6</v>
@@ -2416,30 +2420,30 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
